--- a/AAII_Financials/Quarterly/RYCEY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RYCEY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>RYCEY</t>
   </si>
@@ -656,22 +656,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -681,103 +681,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -820,47 +828,53 @@
       <c r="P8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S8" s="3">
         <v>7444800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>7037900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10799900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9233400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10054400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9760000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11449700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9140000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>10460000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>8354100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9593200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>8388000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>9858800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -903,47 +917,53 @@
       <c r="P9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S9" s="3">
         <v>6929100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>7769900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>10873100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>8060900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>8980900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>18647900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>9232200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>7965900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>8175400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>6811800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>6988500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>6716900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>7418800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -986,47 +1006,53 @@
       <c r="P10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S10" s="3">
         <v>515700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-732000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-73200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1172500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1073500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-8887900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2217500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1174100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2284600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1542300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2604700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1671000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2440000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1082,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1100,47 +1128,53 @@
       <c r="P12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S12" s="3">
         <v>450400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>362300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>425600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>344400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>422100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>392400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>951000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1121900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>633000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>522300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>540000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>532000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1222,8 +1256,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1266,47 +1306,53 @@
       <c r="P14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S14" s="3">
         <v>130500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>482600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-138200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>8500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-342800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-1110900</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>2500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,36 +1395,36 @@
       <c r="P15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S15" s="3">
         <v>222700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>478900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>72000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>64400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>67100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>76900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>103300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>104400</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1388,8 +1434,14 @@
       <c r="AC15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,8 +1468,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1460,47 +1514,53 @@
       <c r="P17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S17" s="3">
         <v>7916900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>9041500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>11934000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>8997900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>10559500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>10267100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>9675100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>9281400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>10700100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>8049000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8129800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>7888900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>8679000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1543,47 +1603,53 @@
       <c r="P18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S18" s="3">
         <v>-472200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2003600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1134100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>235400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-505000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-507100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1774500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-141400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-240200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>305100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1463400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>499100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1179800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,8 +1679,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1657,47 +1725,53 @@
       <c r="P20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S20" s="3">
         <v>3687800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4365700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1115500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1048300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1512700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1039000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1742000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>2173800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-2778500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-3030300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1608200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-48700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1991000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1740,47 +1814,53 @@
       <c r="P21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S21" s="3">
         <v>4363500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4436400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>890900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-131200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1418700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1010300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>4074100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2572000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2481700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2215900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>376900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>950700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-304200</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1823,47 +1903,53 @@
       <c r="P22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S22" s="3">
         <v>126700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>98000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>105500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>113600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>72000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>62600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>43900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>49400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>43100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>54300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>50900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>42100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>39500</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1906,47 +1992,53 @@
       <c r="P23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S23" s="3">
         <v>3089000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-6467200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-124100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-926500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2089700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1608600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3472700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1982900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3061800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2779500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-195600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>408200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-850600</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1989,47 +2081,53 @@
       <c r="P24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S24" s="3">
         <v>325000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>59500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>377200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>135900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-331800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-367600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>273100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>373500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-278300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-488700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>164300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-44800</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,8 +2209,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2155,47 +2259,53 @@
       <c r="P26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S26" s="3">
         <v>2764000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-6526800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-501300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1062400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1757900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1241000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>3199600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1609400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2783400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2290900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-360000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>474000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-805900</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2238,47 +2348,53 @@
       <c r="P27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S27" s="3">
         <v>2765200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-6529300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-503800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1064700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1765200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1243600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3198100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1609400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2783400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2290900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-361300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>474000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-807200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2476,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2404,47 +2526,53 @@
       <c r="P29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S29" s="3">
         <v>62700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-145200</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W29" s="3">
         <v>52500</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-70800</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2654,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,8 +2743,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2653,47 +2793,53 @@
       <c r="P32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S32" s="3">
         <v>-3687800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4365700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1115500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1048300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1512700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1039000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1742000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-2173800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>2778500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>3030300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1608200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>48700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1991000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2736,47 +2882,53 @@
       <c r="P33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S33" s="3">
         <v>2827900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-6674400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-503800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1064700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1712700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1243600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>3127400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1609400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2783400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2290900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-361300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>474000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-625500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,8 +3010,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2902,135 +3060,147 @@
       <c r="P35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S35" s="3">
         <v>2827900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-6674400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-503800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1064700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1712700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1243600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>3127400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1609400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2783400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2290900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-361300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>474000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-625500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3230,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,755 +3263,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8602900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8561900</v>
+      </c>
+      <c r="F41" s="3">
         <v>8403800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8393100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8280600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7808900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6979500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7472200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5458300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5454800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4819900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4617700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3635700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3539400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3141200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4417200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5258900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5512900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4928800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6067800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5708400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4178800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3207800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3412800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2956700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4142500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2081800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>3768700</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>6700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>6700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>117800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>111100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>185300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>198400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>21500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>21500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>10200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>29200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>28500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>15700</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>22300</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>7300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>9100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>4200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>4100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>3700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>2600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>9200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11015000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10962600</v>
+      </c>
+      <c r="F43" s="3">
         <v>10508700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>10495500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>10291800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>9705600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9860200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>10556200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8790900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8785300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8757100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8389700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>8571500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>8344500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>8055900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>9062200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>9570000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>8932500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>8208500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>8272100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>8306500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>8936400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>9961100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>8606400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>9257800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>8174100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>7426700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>7279200</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8161100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8122200</v>
+      </c>
+      <c r="F44" s="3">
         <v>7709300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>7699500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>7687400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>7249400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>6374800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6824800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6886400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6882000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>6175200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5916100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6517900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6345300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5672600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4721800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>5977200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>5360300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5518000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>5229700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>5299100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>5381700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>4807500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3800700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>4091700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3439500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3858200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3644900</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>513500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>511000</v>
+      </c>
+      <c r="F45" s="3">
         <v>632600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>631800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>896000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>845000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>436900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>467800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>247700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>247500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>319700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>306300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>124500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>121200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>262700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>136900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>224500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>91800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>38700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>941800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1141900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>60800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>24700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>12300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>64600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>44300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>65800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32299300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>32145600</v>
+      </c>
+      <c r="F46" s="3">
         <v>31207300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>31167800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>31076900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>29306600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>27074100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>28985400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>24625000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>24609100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23207800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>22234200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>21358200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20792500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>19291500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>18338100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>21030700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>19919800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>18693900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>20518700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>20465100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18562000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>18005300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>15835900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>16372100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>15803000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>13441800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>14732200</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1710200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1702100</v>
+      </c>
+      <c r="F47" s="3">
         <v>1777900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1775700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1766000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1665400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>885100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>947600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1016100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1015400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>973100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>932300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1137400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1107200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1077200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>528500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>553300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>536000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>493100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>529400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>969900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>567500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1222100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1086300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1036800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>794300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>738700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>750600</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6519800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6488800</v>
+      </c>
+      <c r="F48" s="3">
         <v>6422600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6414500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6188500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5836000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5614900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6011300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5626400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5622800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5901300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5653700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6064200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5903600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6020800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7575300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>7632200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>8452300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>8049200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6012900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5858300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6591600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5590300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5066800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>4806700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>4552000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>4361200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>4537700</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2219700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2209100</v>
+      </c>
+      <c r="F49" s="3">
         <v>2240900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2238100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2242800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2115000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2048100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2192700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2157300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2155900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2240500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2146500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2315400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2254100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2311000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>6583600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>6611200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>6752400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>6368400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>6459400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>6864700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>7875100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>7235300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>6256500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>6451100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6058500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>5894000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>6325900</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4149,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,91 +4238,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>544000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>541400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1045800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1044400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2038600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1922500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1009100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1080300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1165200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1164500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1131100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1083600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>801900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>780600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>866300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4744800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>5286200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>4375100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>4367800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5341900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>5042300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5923700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3144600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3207100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3248800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1909500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2133200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2918000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4416,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51752700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>51506300</v>
+      </c>
+      <c r="F54" s="3">
         <v>51298800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>51234000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>51979700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>49018700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>44676200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>47830000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>41719000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>41692100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>40138600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>38454600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>37795900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>36794800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35484100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>37770200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>41113500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>40035700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>37972400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>38862400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>39200300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>39519800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>35197600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>31452600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>31915600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>29117400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>26568900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>29264300</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4542,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,506 +4575,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4232500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4212300</v>
+      </c>
+      <c r="F57" s="3">
         <v>3675600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3671000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3196300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3014300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2526400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2704700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2737400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2735600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2738600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2623700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3290100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3202900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2773700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>8513200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>10295700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>10484800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>9623400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>10115400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>13274500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>9743000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>11146200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>9799800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>9727100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>9029700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>8631600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>8942300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>627600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>624600</v>
+      </c>
+      <c r="F58" s="3">
         <v>1979800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1977300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2918200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2752000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1402200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1501100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>414500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>414300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1076300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1031200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1026800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>999600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>462700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1627700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2203300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>961600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>543500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1046700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1039000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>116000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>233400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>211800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>155100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>546500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>354200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17129200</v>
+        <v>16673700</v>
       </c>
       <c r="E59" s="3">
-        <v>17107600</v>
+        <v>16594400</v>
       </c>
       <c r="F59" s="3">
+        <v>15631200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>15611500</v>
+      </c>
+      <c r="H59" s="3">
         <v>13827900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>13040200</v>
       </c>
-      <c r="H59" s="3">
-        <v>13795000</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>12499200</v>
+      </c>
+      <c r="K59" s="3">
         <v>14768800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13602200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>13593400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13635600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>13063500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12638000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12303300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11647700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7389700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>8147000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>7135800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>7335900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>6954600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2283900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>7732200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1702800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1730400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1354900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1083900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1046800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1087700</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26067400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>25943300</v>
+      </c>
+      <c r="F60" s="3">
         <v>25958300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>25925500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>24959600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23537800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20986000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>22467500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19290500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19278100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19012100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18214400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>18741700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18245200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>16769700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>17530700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>20646100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18582200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>17502700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>18116700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>16597300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>17591200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>13082400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11742100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>11237100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>10660100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>10032600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>10119500</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5174500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5149800</v>
+      </c>
+      <c r="F61" s="3">
         <v>3891000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3886100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3982700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3755900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5190500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5556900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6262100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6258100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6398100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6129600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6362900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6194300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6861900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7751900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8669300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6092300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>7103900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4640500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4750300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>4819900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4671600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3922600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4152500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>3760300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2550600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2887700</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3886200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3867700</v>
+      </c>
+      <c r="F62" s="3">
         <v>4570700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4564900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4911600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4631800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6228300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>6668000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6016900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6013000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6795500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>6510400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>7152000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>6962600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>8622200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>18725800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>21876700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>19522700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>16409900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>17388500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>16848900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>15788400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>12990400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>13492200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>11559000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>8154500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>6861800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>7846800</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5194,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5283,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5372,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47928900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>47700700</v>
+      </c>
+      <c r="F66" s="3">
         <v>47593500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>47533400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>48645000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>45874000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>45779100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>49010900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>44546100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>44517400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>44761000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>42883100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>44106700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>42938400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>42732700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>44036500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>51221900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>44224600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>41044700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>40172500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>38221300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>38203700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>30747100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>29159400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>26951200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>22577600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>19451600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>20860600</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5498,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5583,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5672,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5761,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5850,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>574500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>571800</v>
+      </c>
+      <c r="F72" s="3">
         <v>140000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>139800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>530200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>500000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-5552300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-5944200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-7352700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-7348000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-9186300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-8800900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-10895800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-10607200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-11827200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-10253500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-11878700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-5437200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-4569200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-2957000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>58700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>682100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>3828500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1750100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>4393000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5956800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>6519400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>7779600</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +6028,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +6117,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6206,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3785300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3767300</v>
+      </c>
+      <c r="F76" s="3">
         <v>3668900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3664300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3299100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3111200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-1141800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1222400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-2896600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-2894700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-4688700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-4492000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-6359000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-6190600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-7289600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-6266300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-10108400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-4188900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-3072300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-1310200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>979000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1316100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4450500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2293200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4964400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6539800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>7117200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>8403800</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,96 +6384,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6138,47 +6528,53 @@
       <c r="P81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S81" s="3">
         <v>2827900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-6674400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-503800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1064700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1712700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1243600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>3127400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1609400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2783400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2290900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-361300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>474000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-625500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,91 +6604,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>217800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>205400</v>
+      </c>
+      <c r="F83" s="3">
         <v>141500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>151500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>211100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>210900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>150300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>144000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>238900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>232600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>180700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>167100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>200500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>216900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>184800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1147800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1932900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>909500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>681700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>599000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>535800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>629700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>589100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>537000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>509400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>521700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>500400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6778,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6867,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6956,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +7045,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +7134,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1704900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1696800</v>
+      </c>
+      <c r="F89" s="3">
         <v>1714000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1711800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1382400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1303600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1322700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1416000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1054600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1054000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>993500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>951800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>587700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>572200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>558500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-882900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2877000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2548600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>284600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2003100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>761300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2298100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>255400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1486500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>263700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1781700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-358200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1578800</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,91 +7260,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-157200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-156500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-282000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-281600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-138400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-130500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-241600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-258700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-84000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-84000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-160500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-153800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-112500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-109500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-141000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-520000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-430000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-755000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-408800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-685600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-447100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-493900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-523200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-342400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-396900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-298700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-516200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-767700</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7434,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7523,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-243500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-242300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-337100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-336700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-300000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-282900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-320500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-343100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-201600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-201400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-276400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-264800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-185500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-180600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>510900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-744700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-531000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-933100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-194400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1161300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-30000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-786800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-821200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-831300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-889500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-782600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1931700</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,56 +7649,58 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>276600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>275300</v>
+      </c>
+      <c r="F96" s="3">
         <v>254400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>254100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>347300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>327500</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N96" s="3">
         <v>600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>600</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R96" s="3">
         <v>600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7266,8 +7734,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7823,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7912,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,253 +8001,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1302200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1296000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1299500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1297800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-713800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-673100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-199700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-213800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-460000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-459700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-157300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-150700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-191900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-186800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1210900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>815100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>2961300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1181200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-983900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-157400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1083300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-317000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>211500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-220500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-724000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1025200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-744000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-399000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-13800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-14700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-25300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-25300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-51500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-50100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>34900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>32300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>59500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>64400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-128000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>193500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-120400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-8200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>40300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>43000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-62300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-34300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>161300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>200400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>56100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-64500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>104000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>157800</v>
+      </c>
+      <c r="F102" s="3">
         <v>133900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>133700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>321300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>303000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>788700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>844400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>367800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>367500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>557900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>534500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>158800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>154600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-106600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-940500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-253100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>313900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-901900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>724600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1857600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>847700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-600100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>596100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1149300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2080400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1686800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-647900</v>
       </c>
     </row>
